--- a/media/GRACE.xlsx
+++ b/media/GRACE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sumit\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFCB9B75-955B-4C7E-BBFC-C820A2FB570B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB43CA83-E201-4EDF-B57D-EC9BB8C95DA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{6862F8B6-CA2A-4628-9159-D85C6C9A0D9D}"/>
   </bookViews>
